--- a/diseases/d208/2015-2019.xlsx
+++ b/diseases/d208/2015-2019.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31272,7 +31272,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32058,7 +32058,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33630,7 +33630,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35202,7 +35202,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38346,7 +38346,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39132,7 +39132,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39918,7 +39918,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40704,7 +40704,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41490,7 +41490,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42276,7 +42276,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43062,7 +43062,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44634,7 +44634,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46206,7 +46206,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47778,7 +47778,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">

--- a/diseases/d208/2015-2019.xlsx
+++ b/diseases/d208/2015-2019.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31272,7 +31272,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32058,7 +32058,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33630,7 +33630,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35202,7 +35202,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38346,7 +38346,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39132,7 +39132,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39918,7 +39918,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40704,7 +40704,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41490,7 +41490,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42276,7 +42276,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43062,7 +43062,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44634,7 +44634,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46206,7 +46206,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47778,7 +47778,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
